--- a/files/plan/N100000255.xlsx
+++ b/files/plan/N100000255.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: 충남 고등학교 교육과정 편제표 입력 시스템 저장본(2026-10-22 14:31) · 단위: 학점(창체는 시간)</t>
+          <t>출처: 충남 고등학교 교육과정 편제표 입력 시스템 저장본(2026-10-30 13:30) · 단위: 학점(창체는 시간)</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: 충남 고등학교 교육과정 편제표 입력 시스템 저장본(2026-10-22 14:31) · 단위: 학점(창체는 시간)</t>
+          <t>출처: 충남 고등학교 교육과정 편제표 입력 시스템 저장본(2026-10-30 13:30) · 단위: 학점(창체는 시간)</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: 충남 고등학교 교육과정 편제표 입력 시스템 저장본(2026-10-22 14:31) · 단위: 학점(창체는 시간)</t>
+          <t>출처: 충남 고등학교 교육과정 편제표 입력 시스템 저장본(2026-10-30 13:30) · 단위: 학점(창체는 시간)</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>★ 무용 제작 실습</t>
+          <t>★ 무용 음악 실습</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
